--- a/output/pdf_financials_xlsx/ROMJ.xlsx
+++ b/output/pdf_financials_xlsx/ROMJ.xlsx
@@ -3592,31 +3592,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.902398</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>7.520299</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>11.91947</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>13.815515</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>17.537902</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>20.421908</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>21.624166</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>23.184</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>25.161</v>
       </c>
     </row>
     <row r="93">
@@ -6142,7 +6142,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -8154,7 +8158,11 @@
           <t>Reserves 18</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -10394,7 +10402,11 @@
           <t>Reserves 16 7,520,299</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
         <v>2.902398</v>
       </c>

--- a/output/pdf_financials_xlsx/ROMJ.xlsx
+++ b/output/pdf_financials_xlsx/ROMJ.xlsx
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.628434</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.23242</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.083588</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>12.136459</v>
@@ -1614,13 +1614,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.628434</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.23242</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.083588</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>12.136459</v>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.649727</v>
+        <v>0.021293</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.447737</v>
+        <v>1.215317</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>16.051684</v>
+        <v>13.968096</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>2.913047</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">

--- a/output/pdf_financials_xlsx/ROMJ.xlsx
+++ b/output/pdf_financials_xlsx/ROMJ.xlsx
@@ -931,7 +931,7 @@
         <v>-29.875087</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-14.273794</v>
+        <v>-14.199459</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-14.983172</v>
@@ -965,7 +965,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.074335</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1100,13 +1100,13 @@
         <v>-5.850479</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-29.875087</v>
+        <v>-25.027963</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-14.273794</v>
+        <v>-11.104993</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-14.983172</v>
+        <v>-14.349541</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-14.52074</v>
@@ -1341,7 +1341,7 @@
         <v>-29.875087</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-14.273794</v>
+        <v>-14.199459</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-14.983172</v>
@@ -1409,7 +1409,7 @@
         <v>-29.806769</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-14.200911</v>
+        <v>-14.126576</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-14.860715</v>
@@ -1443,7 +1443,7 @@
         <v>-1469.077229791838</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1347.412990694907</v>
+        <v>-1340.359925953969</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-158.3062578030791</v>
@@ -1477,7 +1477,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.5235058603289041</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.073023</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>0.038713</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.490564</v>
+        <v>0.5635869999999999</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0.20491</v>
@@ -2025,7 +2025,7 @@
         <v>0.021293</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.215317</v>
+        <v>1.142294</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>13.968096</v>
@@ -2584,28 +2584,28 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>1.619985</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>2.020734</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>2.562849</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>1.745266</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>1.572864</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.681248</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.154283</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>1.781021</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -2686,31 +2686,31 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.043907</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.625997</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.973513</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>3.772538</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>2.740851</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>5.262779</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>2.006976</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>3.424</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>3.922</v>
       </c>
     </row>
     <row r="68">
@@ -3806,13 +3806,13 @@
         <v>-5.850479</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-29.875087</v>
+        <v>-25.027963</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-14.273794</v>
+        <v>-11.104993</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-14.983172</v>
+        <v>-14.349541</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-14.52074</v>
@@ -4396,10 +4396,10 @@
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -13689,7 +13689,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -21400,7 +21404,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -22307,7 +22315,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
